--- a/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,13 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster Accessibility" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -61,11 +63,13 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -89,12 +93,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002C5F8A"/>
+        <fgColor rgb="FF2C5F8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,13 +125,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -210,7 +209,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q86" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q97" headerRowCount="1">
   <autoFilter ref="A1:Q86"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
@@ -231,7 +230,7 @@
     <tableColumn id="16" name="Reported by (Partner / IMPACT-default)"/>
     <tableColumn id="17" name="Source channel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -255,7 +254,7 @@
     <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
     <tableColumn id="15" name="Source channel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -551,26 +550,26 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="30" customWidth="1" style="11" min="1" max="1"/>
-    <col width="95" customWidth="1" style="11" min="2" max="2"/>
+    <col width="30" customWidth="1" style="12" min="1" max="1"/>
+    <col width="95" customWidth="1" style="12" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="11">
+    <row r="1" ht="18" customHeight="1" s="12">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>COOPI - NGA MSNA 2026 accessibility report</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.6" customHeight="1" s="11">
+    <row r="3" ht="15.6" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="11">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="12">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>This file lists every ward (and, on the second sheet, every individual cluster) currently assigned to your organisation under the NGA MSNA 2026 sampling design, so you can tell us where your teams are having trouble collecting data and why. We use this to decide how to respond - drawing a replacement cluster where needed - and to correctly document, in our final reporting, which areas' we were able to collect from and which we weren't. Accurate, complete reporting from you feeds directly into that documentation.</t>
         </is>
@@ -583,74 +582,74 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.6" customHeight="1" s="11">
+    <row r="8" ht="15.6" customHeight="1" s="12">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="11">
+    <row r="9" ht="60" customHeight="1" s="12">
       <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Open the 'Ward Accessibility' sheet first - this is your main report, one row per ward you have clusters in. It's pre-filled with every ward/LGA combination assigned to you; you don't need to add or remove rows. Rows are sorted within each LGA by Total target HHs, largest first, so your main wards come before any small border cases.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" s="11">
+    <row r="10" ht="60" customHeight="1" s="12">
       <c r="A10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="11">
+    <row r="11" ht="60" customHeight="1" s="12">
       <c r="A11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" s="11">
+    <row r="12" ht="60" customHeight="1" s="12">
       <c r="A12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="11">
+    <row r="13" ht="60" customHeight="1" s="12">
       <c r="A13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" s="11">
+    <row r="14" ht="60" customHeight="1" s="12">
       <c r="A14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="90" customHeight="1" s="11">
+    <row r="15" ht="90" customHeight="1" s="12">
       <c r="A15" s="5" t="n">
         <v>7</v>
       </c>
@@ -660,7 +659,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.6" customHeight="1" s="11">
+    <row r="17" ht="15.6" customHeight="1" s="12">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
@@ -679,25 +678,25 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1" s="11">
+    <row r="19" ht="45" customHeight="1" s="12">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Ward Accessibility</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1" s="11">
+    <row r="20" ht="45" customHeight="1" s="12">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -717,110 +716,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="1"/>
-    <col width="14" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="19" customWidth="1" style="11" min="4" max="4"/>
-    <col width="30" customWidth="1" style="11" min="5" max="5"/>
-    <col width="30" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="20" customWidth="1" style="11" min="8" max="8"/>
-    <col width="16" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
-    <col width="20" customWidth="1" style="11" min="11" max="11"/>
-    <col width="19" customWidth="1" style="11" min="12" max="12"/>
-    <col width="16" customWidth="1" style="11" min="13" max="13"/>
-    <col width="30" customWidth="1" style="11" min="14" max="14"/>
-    <col width="17" customWidth="1" style="11" min="15" max="15"/>
-    <col width="30" customWidth="1" style="11" min="16" max="16"/>
-    <col width="18" customWidth="1" style="11" min="17" max="17"/>
+    <col width="14" customWidth="1" style="12" min="1" max="2"/>
+    <col width="16" customWidth="1" style="12" min="3" max="3"/>
+    <col width="19" customWidth="1" style="12" min="4" max="4"/>
+    <col width="30" customWidth="1" style="12" min="5" max="6"/>
+    <col width="14" customWidth="1" style="12" min="7" max="7"/>
+    <col width="20" customWidth="1" style="12" min="8" max="8"/>
+    <col width="16" customWidth="1" style="12" min="9" max="9"/>
+    <col width="30" customWidth="1" style="12" min="10" max="10"/>
+    <col width="20" customWidth="1" style="12" min="11" max="11"/>
+    <col width="19" customWidth="1" style="12" min="12" max="12"/>
+    <col width="16" customWidth="1" style="12" min="13" max="13"/>
+    <col width="30" customWidth="1" style="12" min="14" max="14"/>
+    <col width="17" customWidth="1" style="12" min="15" max="15"/>
+    <col width="30" customWidth="1" style="12" min="16" max="16"/>
+    <col width="18" customWidth="1" style="12" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Ward (GRID3)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Ward (OCHA/COD)</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Ward spans multiple LGAs (Y/N)</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Other LGA(s) sharing this ward</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Non-IDP clusters</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>IDP clusters</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Total target HHs (primary)</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="P1" s="13" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="Q1" s="13" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -856,6 +853,11 @@
       <c r="J2" t="n">
         <v>51</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -887,6 +889,11 @@
       <c r="J3" t="n">
         <v>36</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -918,6 +925,11 @@
       <c r="J4" t="n">
         <v>34</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -954,6 +966,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -995,6 +1012,11 @@
       <c r="J6" t="n">
         <v>12</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1026,6 +1048,11 @@
       <c r="J7" t="n">
         <v>12</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1072,6 +1099,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -1123,6 +1155,11 @@
       <c r="J9" t="n">
         <v>6</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1159,6 +1196,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -1200,6 +1242,11 @@
       <c r="J11" t="n">
         <v>6</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1236,6 +1283,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -1277,6 +1329,11 @@
       <c r="J13" t="n">
         <v>4</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1308,6 +1365,11 @@
       <c r="J14" t="n">
         <v>2</v>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1344,6 +1406,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -1385,6 +1452,16 @@
       <c r="J16" t="n">
         <v>50</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1416,6 +1493,11 @@
       <c r="J17" t="n">
         <v>27</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1447,6 +1529,16 @@
       <c r="J18" t="n">
         <v>24</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1478,6 +1570,16 @@
       <c r="J19" t="n">
         <v>18</v>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1509,6 +1611,16 @@
       <c r="J20" t="n">
         <v>18</v>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1540,6 +1652,11 @@
       <c r="J21" t="n">
         <v>14</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1571,6 +1688,11 @@
       <c r="J22" t="n">
         <v>12</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1602,6 +1724,11 @@
       <c r="J23" t="n">
         <v>11</v>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1633,6 +1760,11 @@
       <c r="J24" t="n">
         <v>10</v>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1664,6 +1796,16 @@
       <c r="J25" t="n">
         <v>4</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1695,6 +1837,11 @@
       <c r="J26" t="n">
         <v>3</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1726,6 +1873,11 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1757,6 +1909,11 @@
       <c r="J28" t="n">
         <v>29</v>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1788,6 +1945,11 @@
       <c r="J29" t="n">
         <v>28</v>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1819,6 +1981,11 @@
       <c r="J30" t="n">
         <v>28</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1850,6 +2017,11 @@
       <c r="J31" t="n">
         <v>16</v>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1881,6 +2053,11 @@
       <c r="J32" t="n">
         <v>13</v>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1912,6 +2089,11 @@
       <c r="J33" t="n">
         <v>10</v>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1943,6 +2125,11 @@
       <c r="J34" t="n">
         <v>9</v>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1974,6 +2161,11 @@
       <c r="J35" t="n">
         <v>9</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2005,6 +2197,11 @@
       <c r="J36" t="n">
         <v>6</v>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2036,6 +2233,11 @@
       <c r="J37" t="n">
         <v>6</v>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2067,6 +2269,11 @@
       <c r="J38" t="n">
         <v>6</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2098,6 +2305,11 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2129,6 +2341,11 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2170,6 +2387,16 @@
       <c r="J41" t="n">
         <v>40</v>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2201,6 +2428,11 @@
       <c r="J42" t="n">
         <v>35</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2232,6 +2464,11 @@
       <c r="J43" t="n">
         <v>27</v>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2263,6 +2500,11 @@
       <c r="J44" t="n">
         <v>20</v>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2294,6 +2536,11 @@
       <c r="J45" t="n">
         <v>19</v>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2325,6 +2572,11 @@
       <c r="J46" t="n">
         <v>12</v>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2366,6 +2618,16 @@
       <c r="J47" t="n">
         <v>12</v>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2397,6 +2659,11 @@
       <c r="J48" t="n">
         <v>9</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2438,6 +2705,16 @@
       <c r="J49" t="n">
         <v>8</v>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Physical access (terrain</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2469,6 +2746,11 @@
       <c r="J50" t="n">
         <v>7</v>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2500,6 +2782,11 @@
       <c r="J51" t="n">
         <v>7</v>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2541,6 +2828,16 @@
       <c r="J52" t="n">
         <v>6</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Physical access (terrain</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2572,6 +2869,11 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2613,6 +2915,16 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2644,6 +2956,11 @@
       <c r="J55" t="n">
         <v>55</v>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2675,6 +2992,11 @@
       <c r="J56" t="n">
         <v>33</v>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2706,6 +3028,11 @@
       <c r="J57" t="n">
         <v>29</v>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2737,6 +3064,11 @@
       <c r="J58" t="n">
         <v>22</v>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2768,6 +3100,11 @@
       <c r="J59" t="n">
         <v>18</v>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2799,6 +3136,11 @@
       <c r="J60" t="n">
         <v>12</v>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2830,6 +3172,11 @@
       <c r="J61" t="n">
         <v>11</v>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2861,6 +3208,11 @@
       <c r="J62" t="n">
         <v>6</v>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2892,6 +3244,11 @@
       <c r="J63" t="n">
         <v>6</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2923,6 +3280,11 @@
       <c r="J64" t="n">
         <v>6</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2954,6 +3316,11 @@
       <c r="J65" t="n">
         <v>6</v>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2985,6 +3352,11 @@
       <c r="J66" t="n">
         <v>0</v>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3016,6 +3388,11 @@
       <c r="J67" t="n">
         <v>59</v>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3047,6 +3424,11 @@
       <c r="J68" t="n">
         <v>13</v>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3078,6 +3460,16 @@
       <c r="J69" t="n">
         <v>12</v>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3109,6 +3501,11 @@
       <c r="J70" t="n">
         <v>12</v>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3140,6 +3537,11 @@
       <c r="J71" t="n">
         <v>10</v>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3171,6 +3573,16 @@
       <c r="J72" t="n">
         <v>10</v>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3202,6 +3614,11 @@
       <c r="J73" t="n">
         <v>10</v>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3233,6 +3650,11 @@
       <c r="J74" t="n">
         <v>9</v>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3264,6 +3686,11 @@
       <c r="J75" t="n">
         <v>7</v>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3295,6 +3722,11 @@
       <c r="J76" t="n">
         <v>7</v>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3326,6 +3758,11 @@
       <c r="J77" t="n">
         <v>7</v>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3367,6 +3804,11 @@
       <c r="J78" t="n">
         <v>6</v>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3398,6 +3840,11 @@
       <c r="J79" t="n">
         <v>6</v>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3429,6 +3876,16 @@
       <c r="J80" t="n">
         <v>6</v>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3460,6 +3917,11 @@
       <c r="J81" t="n">
         <v>6</v>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3491,6 +3953,11 @@
       <c r="J82" t="n">
         <v>5</v>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3522,6 +3989,11 @@
       <c r="J83" t="n">
         <v>5</v>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3553,6 +4025,11 @@
       <c r="J84" t="n">
         <v>4</v>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3584,6 +4061,11 @@
       <c r="J85" t="n">
         <v>3</v>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3625,20 +4107,441 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Asso</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>6</v>
+      </c>
+      <c r="O87" s="13" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chakfem</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="13" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chanso</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="13" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Gindiri 1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="13" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Jipal</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="13" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Kadunu</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="13" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Kasuwan Ali</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="13" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kombun</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="13" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Panyam South</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="13" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="13" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mbaya</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Buruku</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>6</v>
+      </c>
+      <c r="O97" s="13" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="K2:K86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="K2:K86 K87:K96 K97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L86 L87:L96 L97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P86 P87:P96 P97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q86 Q87:Q96 Q97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O87:O96 O97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3655,97 +4558,95 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="1"/>
-    <col width="14" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="14" customWidth="1" style="11" min="4" max="4"/>
-    <col width="14" customWidth="1" style="11" min="5" max="5"/>
-    <col width="16" customWidth="1" style="11" min="6" max="6"/>
-    <col width="24" customWidth="1" style="11" min="7" max="7"/>
-    <col width="15" customWidth="1" style="11" min="8" max="8"/>
-    <col width="20" customWidth="1" style="11" min="9" max="9"/>
-    <col width="19" customWidth="1" style="11" min="10" max="10"/>
-    <col width="16" customWidth="1" style="11" min="11" max="11"/>
-    <col width="30" customWidth="1" style="11" min="12" max="12"/>
-    <col width="17" customWidth="1" style="11" min="13" max="13"/>
-    <col width="30" customWidth="1" style="11" min="14" max="14"/>
-    <col width="18" customWidth="1" style="11" min="15" max="15"/>
+    <col width="14" customWidth="1" style="12" min="1" max="2"/>
+    <col width="16" customWidth="1" style="12" min="3" max="3"/>
+    <col width="14" customWidth="1" style="12" min="4" max="5"/>
+    <col width="16" customWidth="1" style="12" min="6" max="6"/>
+    <col width="24" customWidth="1" style="12" min="7" max="7"/>
+    <col width="15" customWidth="1" style="12" min="8" max="8"/>
+    <col width="20" customWidth="1" style="12" min="9" max="9"/>
+    <col width="19" customWidth="1" style="12" min="10" max="10"/>
+    <col width="16" customWidth="1" style="12" min="11" max="11"/>
+    <col width="30" customWidth="1" style="12" min="12" max="12"/>
+    <col width="17" customWidth="1" style="12" min="13" max="13"/>
+    <col width="30" customWidth="1" style="12" min="14" max="14"/>
+    <col width="18" customWidth="1" style="12" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Ward (GRID3)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Pop Type</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cluster ID</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -4427,6 +5328,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4512,6 +5418,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4597,6 +5508,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4647,6 +5563,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4697,6 +5618,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4747,6 +5673,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4797,6 +5728,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4891,6 +5827,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -4948,6 +5889,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5047,6 +5993,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5099,6 +6050,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5225,6 +6181,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5277,6 +6238,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5329,6 +6295,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5455,6 +6426,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5544,6 +6520,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -5633,6 +6614,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -6188,7 +7174,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6245,7 +7231,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6302,7 +7288,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6357,6 +7343,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6399,6 +7390,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6441,6 +7437,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6478,6 +7479,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6515,6 +7521,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6554,7 +7565,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6606,7 +7617,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6656,6 +7667,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6693,6 +7709,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6730,6 +7751,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7658,6 +8684,16 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7705,6 +8741,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr">
         <is>
           <t>Partner</t>
@@ -7802,6 +8843,11 @@
       <c r="I97" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -8472,8 +9518,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a2915931200ea69f6d4702d545d15c4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebf5164e0bbea30cbcbeb97056918f83" ns2:_="" ns3:_="">
     <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
     <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
     <xsd:element name="properties">
@@ -8521,7 +9567,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -8580,7 +9626,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -8599,7 +9645,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -8616,8 +9662,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -8727,13 +9773,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42D2F8F5-6825-4010-9078-C86793B8F6FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB669CFD-A58B-4F3B-BC17-42C7C5B68D2E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE77C861-2F8C-442E-8989-20EE21EAE692}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36D8B6A-883D-4FEB-B0D9-E9B08128A2F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C93F85E2-5F93-4342-917D-463552ACD5E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3512E58A-4698-4A87-B15C-16F4194866F6}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q97" headerRowCount="1">
-  <autoFilter ref="A1:Q86"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q170" headerRowCount="1">
+  <autoFilter ref="A1:Q170"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:Q170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -4525,23 +4525,2831 @@
       </c>
       <c r="O97" s="13" t="n"/>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Agan</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Makurdi</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Agbashi</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Akwana</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Amiri</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Iwagu</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mbanyaber</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Obene</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tombo</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Agban</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Arak</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Karshi</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Kukum</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Madakiya</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Nandu</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Nduya</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Samban</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chikaji</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hanwa</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Igabi</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Jushi</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Kerawa</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Maigana</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Panhauya</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Richifa</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Wazata</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Zangon Aya</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Batagarawa; Rimi</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Bugaje</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Batagarawa; Jibia</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Dandagoro</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Batagarawa; Rimi</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Kayauki</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Batagarawa; Kaita; Rimi</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Kusa</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Riko</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Jibia; Kaita</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Bokkos Central</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bwall</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Doka East</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Doka West</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Fier</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Fursum East</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Goechim</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Jiblik</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Kagu</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Kangshu</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Kapwis</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Kardam B</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Kardam C</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Kwa</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Kwatas</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Barikin Ladi; Bokkos</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lankan</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Latok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lere North</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lobring</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Majuju Doss</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Marit</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mushere Central</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Tafan B</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Tangur</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Bokkos</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tapshin</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Aboro</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Barikin Ladi; Bokkos</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Atuku</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Chugwi</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Gassa</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Gidan Waya</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Heipang</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Kamaru</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Karshi</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Manchok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Pari</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Pwomo / Chit</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Sho</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Barikin Ladi</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Vwang</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Zankan</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K86 K87:K96 K97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L86 L87:L96 L97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P86 P87:P96 P97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q86 Q87:Q96 Q97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O87:O96 O97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+    <dataValidation sqref="O2:O170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9518,8 +12326,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a2915931200ea69f6d4702d545d15c4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebf5164e0bbea30cbcbeb97056918f83" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
     <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
     <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
     <xsd:element name="properties">
@@ -9567,7 +12375,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -9626,7 +12434,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -9645,7 +12453,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -9662,8 +12470,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -9773,13 +12581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB669CFD-A58B-4F3B-BC17-42C7C5B68D2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B261DC0A-20A3-4B5E-B16E-8D289F20B79A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36D8B6A-883D-4FEB-B0D9-E9B08128A2F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E701D3F-2396-439C-AE36-4599FAB5768E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3512E58A-4698-4A87-B15C-16F4194866F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6936D673-A31D-446D-93F3-CB9286735319}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
@@ -235,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O114" headerRowCount="1">
-  <autoFilter ref="A1:O114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O163" headerRowCount="1">
+  <autoFilter ref="A1:O163"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -4587,7 +4587,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4665,7 +4664,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4702,7 +4700,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4739,7 +4736,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4776,7 +4772,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4813,7 +4808,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4891,7 +4885,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4928,7 +4921,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -4965,7 +4957,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5002,7 +4993,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5039,7 +5029,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5076,7 +5065,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5113,7 +5101,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5150,7 +5137,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5187,7 +5173,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5224,7 +5209,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5261,7 +5245,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5298,7 +5281,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5335,7 +5317,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5372,7 +5353,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5409,7 +5389,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5446,7 +5425,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5483,7 +5461,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5520,7 +5497,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5557,7 +5533,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5881,7 +5856,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5918,7 +5892,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5955,7 +5928,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -5992,7 +5964,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6111,7 +6082,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6148,7 +6118,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6185,7 +6154,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6263,7 +6231,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6300,7 +6267,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6337,7 +6303,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6415,7 +6380,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6452,7 +6416,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6489,7 +6452,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6567,7 +6529,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6768,7 +6729,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6846,7 +6806,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -6965,7 +6924,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -7084,7 +7042,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -7121,7 +7078,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -7158,7 +7114,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -7318,7 +7273,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -7365,7 +7319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -12303,18 +12257,1968 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fiidi</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp1</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mbawa</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp2</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mbawa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp3</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mbabai</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp4</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mbawa</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp5</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Mbawa</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp6</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Uvir</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>non_idp_NG007006_supp7</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Barde</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp1</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Asso</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp4</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Kafanchan A</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp5</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Maigizo</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp8</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Asso</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp9</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Kaninkon</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp11</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>non_idp_NG021021_supp1</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Gabas 3</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>non_idp_NG021021_supp2</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Yamma 1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>non_idp_NG021021_supp3</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Asso</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp13</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Asso</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp14</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Arak</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp15</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Jema'a</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Kaninkon</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>non_idp_NG019007_supp16</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Arewa 2</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>non_idp_NG021021_supp5</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Dutsen Abba</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>non_idp_NG019023_supp1</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Kufena</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>non_idp_NG019023_supp2</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Wuciciri</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>non_idp_NG019023_supp3</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Dutsen Abba</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>non_idp_NG019023_supp4</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Dambo</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>non_idp_NG019023_supp5</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Dutsen Abba</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>non_idp_NG019023_supp6</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Nyiev</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>idp_NG007006_supp1</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Nzorov</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>idp_NG007006_supp2</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Benue</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Guma</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Nzorov</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>idp_NG007006_supp3</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Zaria</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Limancin Kona</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>idp_NG019023_supp1</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Kudu 3</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>idp_NG021021_supp1</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Kudu 3</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>idp_NG021021_supp2</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Kudu 3</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>idp_NG021021_supp3</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Yamma 2</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>idp_NG021021_supp4</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Arewa 1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>idp_NG021021_supp5</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Gabas 3</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>idp_NG021021_supp6</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ampang</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp1</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kombun</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp2</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Pushit</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp3</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mangu 1</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp4</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Mangu 11</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp5</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Mangu 11</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp6</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Mangu</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Mangu 11</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>idp_NG032011_supp7</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ta Hoss</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>idp_NG032015_supp1</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Turu B</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>idp_NG032015_supp2</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Sopp</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>idp_NG032015_supp3</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Kwi</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>idp_NG032015_supp4</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Riyom</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Kwi</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>idp_NG032015_supp5</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12581,13 +14485,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B261DC0A-20A3-4B5E-B16E-8D289F20B79A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12906FB3-721E-4CF7-8981-7906204EB7BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E701D3F-2396-439C-AE36-4599FAB5768E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5C5C3D-FB40-4305-A075-7A78396EEAD5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6936D673-A31D-446D-93F3-CB9286735319}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFEAB91-A756-4B90-9F91-8E3C88AC0182}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
@@ -14227,271 +14227,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12906FB3-721E-4CF7-8981-7906204EB7BE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5C5C3D-FB40-4305-A075-7A78396EEAD5}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FFEAB91-A756-4B90-9F91-8E3C88AC0182}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/COOPI_accessibility_report.xlsx
@@ -14227,4 +14227,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EB77AAE-E0EC-4912-8E99-32141B36BE92}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67B0C95A-5A68-456E-B1A0-C1B3763060A7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B9DB5B-267B-42DB-8F4C-09842BC4293C}"/>
 </file>